--- a/Excel/Ejercicio_Calibracion_2026-05-04_10-05.xlsx
+++ b/Excel/Ejercicio_Calibracion_2026-05-04_10-05.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Repetibilidad" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Excentricidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Excentricidad 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Excentricidad 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Excentricidad 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Excentricidad 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Excentricidad 6" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -904,4 +910,2089 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="n">
+        <v>756.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>603.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="n">
+        <v>603.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Pesas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Serie</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Juego</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Id_pesa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JGMBE-014</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JGMBE-012</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IND131</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JGMBE-013</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Parámetro Ambiental</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Condición Inicial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Condición Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Modelos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>603.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="n">
+        <v>603.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Pesas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Serie</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Juego</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Id_pesa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JGMBE-014</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JGMBE-012</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IND131</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JGMBE-013</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Parámetro Ambiental</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Condición Inicial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Condición Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fluke, A98314, A89174</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Druck, 2791794, 2791794</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fluke, N20111, A89386</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Valor (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Der.-Izq.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Izq.-Der.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Promedios por Sección</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promedio (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1214.5</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Pesas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Serie</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Juego</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Id_pesa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sin modelo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sin serie</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LGM-03</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>masa y masa convencional</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JGMBE-012</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IND131</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Medidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Valor Inicial (Ci)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hora Inicial</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Valor Final (Cf)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Hora Final</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.00 Pa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14:04:03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.00 Pa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>14:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Humedad</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.0 %</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>14:04:03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.0 %</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>14:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0 °C</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:04:03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.0 °C</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>14:04:03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>